--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.87379385769623</v>
+        <v>5.829491501875639</v>
       </c>
       <c r="D2" t="n">
-        <v>30.81253113263782</v>
+        <v>5.007036309053646</v>
       </c>
       <c r="E2" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F2" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.51512570550415</v>
+        <v>7.396207927144426</v>
       </c>
       <c r="D3" t="n">
-        <v>45.5187177736068</v>
+        <v>7.396791638211106</v>
       </c>
       <c r="E3" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F3" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.35833088587276</v>
+        <v>2.008228768954323</v>
       </c>
       <c r="D4" t="n">
-        <v>12.21493089283141</v>
+        <v>1.984926270085104</v>
       </c>
       <c r="E4" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F4" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.8973413355881</v>
+        <v>10.54581796703307</v>
       </c>
       <c r="D5" t="n">
-        <v>64.92518751734515</v>
+        <v>10.55034297156859</v>
       </c>
       <c r="E5" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F5" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.9476875952012</v>
+        <v>3.078999234220194</v>
       </c>
       <c r="D6" t="n">
-        <v>18.31792797400325</v>
+        <v>2.976663295775528</v>
       </c>
       <c r="E6" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F6" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.414377552511684</v>
+        <v>1.529836352283149</v>
       </c>
       <c r="D7" t="n">
-        <v>9.277941612449673</v>
+        <v>1.507665512023072</v>
       </c>
       <c r="E7" t="n">
-        <v>19.75690915230392</v>
+        <v>3.210497737249387</v>
       </c>
       <c r="F7" t="n">
-        <v>19.76213927627774</v>
+        <v>3.211347632395132</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
